--- a/project/templates/BD_template.xlsx
+++ b/project/templates/BD_template.xlsx
@@ -456,7 +456,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -712,6 +712,7 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1166,7 +1167,7 @@
     <row r="18" ht="22.05" customHeight="1">
       <c r="A18" s="47" t="inlineStr">
         <is>
-          <t>SHIPMENT FROM HONG KONG TO DHAKA BY AIR</t>
+          <t>SHIPMENT TO:</t>
         </is>
       </c>
       <c r="K18" s="3" t="n"/>
@@ -1476,8 +1477,8 @@
         </is>
       </c>
       <c r="G40" s="95" t="n"/>
-      <c r="H40" s="96" t="n"/>
-      <c r="I40" s="96" t="n"/>
+      <c r="H40" s="97" t="n"/>
+      <c r="I40" s="97" t="n"/>
       <c r="J40" s="11" t="n"/>
       <c r="K40" s="11" t="n"/>
       <c r="L40" s="5" t="n"/>
